--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260810.xlsx
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>75,792,801</t>
+          <t>34,186,338</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>34,186,338</t>
+          <t>75,792,801</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>79,627,193</t>
+          <t>201,602,619</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>201,602,619</t>
+          <t>79,627,193</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
